--- a/HIV_Study_Template.xlsx
+++ b/HIV_Study_Template.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/e2777c86b94f1aa8/Desktop/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="299" documentId="11_45542CE213E66E7193FD27ED2AC063BE36D277C7" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{6C78B5F5-3B13-435F-B556-D07EF070C5D5}"/>
+  <xr:revisionPtr revIDLastSave="319" documentId="11_45542CE213E66E7193FD27ED2AC063BE36D277C7" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{8A0D3CF0-3CE0-41D3-AE1E-C88EE1E4C9B7}"/>
   <bookViews>
-    <workbookView xWindow="32745" yWindow="2850" windowWidth="25800" windowHeight="15525" firstSheet="1" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="4695" yWindow="2535" windowWidth="25800" windowHeight="15525" firstSheet="2" activeTab="7" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="StudyMeta" sheetId="1" r:id="rId1"/>
@@ -41,7 +41,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1557" uniqueCount="733">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1558" uniqueCount="734">
   <si>
     <t>Field</t>
   </si>
@@ -2240,6 +2240,9 @@
   </si>
   <si>
     <t>May 4-May 15 2026</t>
+  </si>
+  <si>
+    <t xml:space="preserve">tier </t>
   </si>
 </sst>
 </file>
@@ -2290,7 +2293,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="2">
+  <borders count="3">
     <border>
       <left/>
       <right/>
@@ -2313,6 +2316,17 @@
       </bottom>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin">
+        <color rgb="FF334155"/>
+      </left>
+      <right style="thin">
+        <color rgb="FF334155"/>
+      </right>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
@@ -2330,7 +2344,9 @@
     <xf numFmtId="9" fontId="0" fillId="0" borderId="0" xfId="1" applyFont="1"/>
     <xf numFmtId="9" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="16" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -2860,445 +2876,445 @@
         <v>31</v>
       </c>
     </row>
-    <row r="11" spans="1:6" s="9" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A11" s="9">
+    <row r="11" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A11">
         <v>3</v>
       </c>
-      <c r="B11" s="9">
-        <v>0</v>
-      </c>
-      <c r="C11" s="9" t="s">
+      <c r="B11">
+        <v>0</v>
+      </c>
+      <c r="C11" t="s">
         <v>34</v>
       </c>
-      <c r="E11" s="9" t="s">
+      <c r="E11" t="s">
         <v>35</v>
       </c>
-      <c r="F11" s="9" t="s">
+      <c r="F11" t="s">
         <v>36</v>
       </c>
     </row>
-    <row r="12" spans="1:6" s="9" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A12" s="9">
+    <row r="12" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A12">
         <v>3</v>
       </c>
-      <c r="B12" s="9">
+      <c r="B12">
         <v>1</v>
       </c>
-      <c r="C12" s="9" t="s">
+      <c r="C12" t="s">
         <v>34</v>
       </c>
-      <c r="E12" s="9" t="s">
+      <c r="E12" t="s">
         <v>37</v>
       </c>
-      <c r="F12" s="9" t="s">
+      <c r="F12" t="s">
         <v>36</v>
       </c>
     </row>
-    <row r="13" spans="1:6" s="9" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A13" s="9">
+    <row r="13" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A13">
         <v>3</v>
       </c>
-      <c r="B13" s="9">
+      <c r="B13">
         <v>2</v>
       </c>
-      <c r="C13" s="9" t="s">
+      <c r="C13" t="s">
         <v>34</v>
       </c>
-      <c r="E13" s="9" t="s">
+      <c r="E13" t="s">
         <v>38</v>
       </c>
-      <c r="F13" s="9" t="s">
+      <c r="F13" t="s">
         <v>36</v>
       </c>
     </row>
-    <row r="14" spans="1:6" s="9" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A14" s="9">
+    <row r="14" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A14">
         <v>4</v>
       </c>
-      <c r="B14" s="9">
-        <v>0</v>
-      </c>
-      <c r="C14" s="9" t="s">
+      <c r="B14">
+        <v>0</v>
+      </c>
+      <c r="C14" t="s">
         <v>39</v>
       </c>
-      <c r="E14" s="9" t="s">
+      <c r="E14" t="s">
         <v>40</v>
       </c>
-      <c r="F14" s="9" t="s">
+      <c r="F14" t="s">
         <v>41</v>
       </c>
     </row>
-    <row r="15" spans="1:6" s="9" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A15" s="9">
+    <row r="15" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A15">
         <v>4</v>
       </c>
-      <c r="B15" s="9">
+      <c r="B15">
         <v>1</v>
       </c>
-      <c r="C15" s="9" t="s">
+      <c r="C15" t="s">
         <v>39</v>
       </c>
-      <c r="E15" s="9" t="s">
+      <c r="E15" t="s">
         <v>42</v>
       </c>
-      <c r="F15" s="9" t="s">
+      <c r="F15" t="s">
         <v>41</v>
       </c>
     </row>
-    <row r="16" spans="1:6" s="9" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A16" s="9">
+    <row r="16" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A16">
         <v>4</v>
       </c>
-      <c r="B16" s="9">
+      <c r="B16">
         <v>2</v>
       </c>
-      <c r="C16" s="9" t="s">
+      <c r="C16" t="s">
         <v>39</v>
       </c>
-      <c r="E16" s="9" t="s">
+      <c r="E16" t="s">
         <v>43</v>
       </c>
-      <c r="F16" s="9" t="s">
+      <c r="F16" t="s">
         <v>41</v>
       </c>
     </row>
-    <row r="17" spans="1:6" s="9" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A17" s="9">
+    <row r="17" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A17">
         <v>5</v>
       </c>
-      <c r="B17" s="9">
-        <v>0</v>
-      </c>
-      <c r="C17" s="9" t="s">
+      <c r="B17">
+        <v>0</v>
+      </c>
+      <c r="C17" t="s">
         <v>44</v>
       </c>
-      <c r="E17" s="9" t="s">
+      <c r="E17" t="s">
         <v>45</v>
       </c>
-      <c r="F17" s="9" t="s">
+      <c r="F17" t="s">
         <v>46</v>
       </c>
     </row>
-    <row r="18" spans="1:6" s="9" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A18" s="9">
+    <row r="18" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A18">
         <v>5</v>
       </c>
-      <c r="B18" s="9">
+      <c r="B18">
         <v>1</v>
       </c>
-      <c r="C18" s="9" t="s">
+      <c r="C18" t="s">
         <v>44</v>
       </c>
-      <c r="E18" s="9" t="s">
+      <c r="E18" t="s">
         <v>47</v>
       </c>
-      <c r="F18" s="9" t="s">
+      <c r="F18" t="s">
         <v>46</v>
       </c>
     </row>
-    <row r="19" spans="1:6" s="9" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A19" s="9">
+    <row r="19" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A19">
         <v>6</v>
       </c>
-      <c r="B19" s="9">
-        <v>0</v>
-      </c>
-      <c r="C19" s="9" t="s">
+      <c r="B19">
+        <v>0</v>
+      </c>
+      <c r="C19" t="s">
         <v>48</v>
       </c>
-      <c r="E19" s="9" t="s">
+      <c r="E19" t="s">
         <v>49</v>
       </c>
-      <c r="F19" s="9" t="s">
+      <c r="F19" t="s">
         <v>50</v>
       </c>
     </row>
-    <row r="20" spans="1:6" s="9" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A20" s="9">
+    <row r="20" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A20">
         <v>6</v>
       </c>
-      <c r="B20" s="9">
+      <c r="B20">
         <v>1</v>
       </c>
-      <c r="C20" s="9" t="s">
+      <c r="C20" t="s">
         <v>48</v>
       </c>
-      <c r="E20" s="9" t="s">
+      <c r="E20" t="s">
         <v>51</v>
       </c>
-      <c r="F20" s="9" t="s">
+      <c r="F20" t="s">
         <v>50</v>
       </c>
     </row>
-    <row r="21" spans="1:6" s="9" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A21" s="9">
+    <row r="21" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A21">
         <v>6</v>
       </c>
-      <c r="B21" s="9">
+      <c r="B21">
         <v>2</v>
       </c>
-      <c r="C21" s="9" t="s">
+      <c r="C21" t="s">
         <v>48</v>
       </c>
-      <c r="E21" s="9" t="s">
+      <c r="E21" t="s">
         <v>52</v>
       </c>
-      <c r="F21" s="9" t="s">
+      <c r="F21" t="s">
         <v>50</v>
       </c>
     </row>
-    <row r="22" spans="1:6" s="9" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A22" s="9">
+    <row r="22" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A22">
         <v>7</v>
       </c>
-      <c r="B22" s="9">
-        <v>0</v>
-      </c>
-      <c r="C22" s="9" t="s">
+      <c r="B22">
+        <v>0</v>
+      </c>
+      <c r="C22" t="s">
         <v>53</v>
       </c>
-      <c r="E22" s="9" t="s">
+      <c r="E22" t="s">
         <v>54</v>
       </c>
-      <c r="F22" s="9" t="s">
+      <c r="F22" t="s">
         <v>55</v>
       </c>
     </row>
-    <row r="23" spans="1:6" s="9" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A23" s="9">
+    <row r="23" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A23">
         <v>8</v>
       </c>
-      <c r="B23" s="9">
-        <v>0</v>
-      </c>
-      <c r="C23" s="9" t="s">
+      <c r="B23">
+        <v>0</v>
+      </c>
+      <c r="C23" t="s">
         <v>56</v>
       </c>
-      <c r="E23" s="9" t="s">
+      <c r="E23" t="s">
         <v>57</v>
       </c>
-      <c r="F23" s="9" t="s">
+      <c r="F23" t="s">
         <v>58</v>
       </c>
     </row>
-    <row r="24" spans="1:6" s="9" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A24" s="9">
+    <row r="24" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A24">
         <v>9</v>
       </c>
-      <c r="B24" s="9">
-        <v>0</v>
-      </c>
-      <c r="C24" s="9" t="s">
+      <c r="B24">
+        <v>0</v>
+      </c>
+      <c r="C24" t="s">
         <v>59</v>
       </c>
-      <c r="E24" s="9" t="s">
+      <c r="E24" t="s">
         <v>60</v>
       </c>
-      <c r="F24" s="9" t="s">
+      <c r="F24" t="s">
         <v>61</v>
       </c>
     </row>
-    <row r="25" spans="1:6" s="9" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A25" s="9">
+    <row r="25" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A25">
         <v>10</v>
       </c>
-      <c r="B25" s="9">
-        <v>0</v>
-      </c>
-      <c r="C25" s="9" t="s">
+      <c r="B25">
+        <v>0</v>
+      </c>
+      <c r="C25" t="s">
         <v>62</v>
       </c>
-      <c r="E25" s="9" t="s">
+      <c r="E25" t="s">
         <v>63</v>
       </c>
-      <c r="F25" s="9" t="s">
+      <c r="F25" t="s">
         <v>64</v>
       </c>
     </row>
-    <row r="26" spans="1:6" s="9" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A26" s="9">
+    <row r="26" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A26">
         <v>10</v>
       </c>
-      <c r="B26" s="9">
+      <c r="B26">
         <v>1</v>
       </c>
-      <c r="C26" s="9" t="s">
+      <c r="C26" t="s">
         <v>62</v>
       </c>
-      <c r="E26" s="9" t="s">
+      <c r="E26" t="s">
         <v>65</v>
       </c>
-      <c r="F26" s="9" t="s">
+      <c r="F26" t="s">
         <v>64</v>
       </c>
     </row>
-    <row r="27" spans="1:6" s="9" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A27" s="9">
+    <row r="27" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A27">
         <v>11</v>
       </c>
-      <c r="B27" s="9">
-        <v>0</v>
-      </c>
-      <c r="C27" s="9" t="s">
+      <c r="B27">
+        <v>0</v>
+      </c>
+      <c r="C27" t="s">
         <v>66</v>
       </c>
-      <c r="E27" s="9" t="s">
+      <c r="E27" t="s">
         <v>67</v>
       </c>
-      <c r="F27" s="9" t="s">
+      <c r="F27" t="s">
         <v>68</v>
       </c>
     </row>
-    <row r="28" spans="1:6" s="9" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A28" s="9">
+    <row r="28" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A28">
         <v>11</v>
       </c>
-      <c r="B28" s="9">
+      <c r="B28">
         <v>1</v>
       </c>
-      <c r="C28" s="9" t="s">
+      <c r="C28" t="s">
         <v>66</v>
       </c>
-      <c r="E28" s="9" t="s">
+      <c r="E28" t="s">
         <v>69</v>
       </c>
-      <c r="F28" s="9" t="s">
+      <c r="F28" t="s">
         <v>68</v>
       </c>
     </row>
-    <row r="29" spans="1:6" s="9" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A29" s="9">
+    <row r="29" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A29">
         <v>12</v>
       </c>
-      <c r="B29" s="9">
-        <v>0</v>
-      </c>
-      <c r="C29" s="9" t="s">
+      <c r="B29">
+        <v>0</v>
+      </c>
+      <c r="C29" t="s">
         <v>70</v>
       </c>
-      <c r="E29" s="9" t="s">
+      <c r="E29" t="s">
         <v>71</v>
       </c>
-      <c r="F29" s="9" t="s">
+      <c r="F29" t="s">
         <v>72</v>
       </c>
     </row>
-    <row r="30" spans="1:6" s="9" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A30" s="9">
+    <row r="30" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A30">
         <v>12</v>
       </c>
-      <c r="B30" s="9">
+      <c r="B30">
         <v>1</v>
       </c>
-      <c r="C30" s="9" t="s">
+      <c r="C30" t="s">
         <v>70</v>
       </c>
-      <c r="E30" s="9" t="s">
+      <c r="E30" t="s">
         <v>73</v>
       </c>
-      <c r="F30" s="9" t="s">
+      <c r="F30" t="s">
         <v>72</v>
       </c>
     </row>
-    <row r="31" spans="1:6" s="9" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A31" s="9">
+    <row r="31" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A31">
         <v>13</v>
       </c>
-      <c r="B31" s="9">
-        <v>0</v>
-      </c>
-      <c r="C31" s="9" t="s">
+      <c r="B31">
+        <v>0</v>
+      </c>
+      <c r="C31" t="s">
         <v>74</v>
       </c>
-      <c r="E31" s="9" t="s">
+      <c r="E31" t="s">
         <v>75</v>
       </c>
-      <c r="F31" s="9" t="s">
+      <c r="F31" t="s">
         <v>76</v>
       </c>
     </row>
-    <row r="32" spans="1:6" s="9" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A32" s="9">
+    <row r="32" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A32">
         <v>13</v>
       </c>
-      <c r="B32" s="9">
+      <c r="B32">
         <v>1</v>
       </c>
-      <c r="C32" s="9" t="s">
+      <c r="C32" t="s">
         <v>74</v>
       </c>
-      <c r="E32" s="9" t="s">
+      <c r="E32" t="s">
         <v>77</v>
       </c>
-      <c r="F32" s="9" t="s">
+      <c r="F32" t="s">
         <v>76</v>
       </c>
     </row>
-    <row r="33" spans="1:6" s="9" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A33" s="9">
+    <row r="33" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A33">
         <v>13</v>
       </c>
-      <c r="B33" s="9">
+      <c r="B33">
         <v>2</v>
       </c>
-      <c r="C33" s="9" t="s">
+      <c r="C33" t="s">
         <v>74</v>
       </c>
-      <c r="E33" s="9" t="s">
+      <c r="E33" t="s">
         <v>78</v>
       </c>
-      <c r="F33" s="9" t="s">
+      <c r="F33" t="s">
         <v>76</v>
       </c>
     </row>
-    <row r="34" spans="1:6" s="9" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A34" s="9">
+    <row r="34" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A34">
         <v>14</v>
       </c>
-      <c r="B34" s="9">
-        <v>0</v>
-      </c>
-      <c r="C34" s="9" t="s">
+      <c r="B34">
+        <v>0</v>
+      </c>
+      <c r="C34" t="s">
         <v>79</v>
       </c>
-      <c r="E34" s="9" t="s">
+      <c r="E34" t="s">
         <v>80</v>
       </c>
-      <c r="F34" s="9" t="s">
+      <c r="F34" t="s">
         <v>81</v>
       </c>
     </row>
-    <row r="35" spans="1:6" s="9" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A35" s="9">
+    <row r="35" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A35">
         <v>15</v>
       </c>
-      <c r="B35" s="9">
-        <v>0</v>
-      </c>
-      <c r="C35" s="9" t="s">
+      <c r="B35">
+        <v>0</v>
+      </c>
+      <c r="C35" t="s">
         <v>82</v>
       </c>
-      <c r="E35" s="9" t="s">
+      <c r="E35" t="s">
         <v>83</v>
       </c>
-      <c r="F35" s="9" t="s">
+      <c r="F35" t="s">
         <v>84</v>
       </c>
     </row>
-    <row r="36" spans="1:6" s="9" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A36" s="9">
+    <row r="36" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A36">
         <v>15</v>
       </c>
-      <c r="B36" s="9">
+      <c r="B36">
         <v>1</v>
       </c>
-      <c r="C36" s="9" t="s">
+      <c r="C36" t="s">
         <v>82</v>
       </c>
-      <c r="E36" s="9" t="s">
+      <c r="E36" t="s">
         <v>85</v>
       </c>
-      <c r="F36" s="9" t="s">
+      <c r="F36" t="s">
         <v>84</v>
       </c>
     </row>
@@ -7555,10 +7571,13 @@
 
 <file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0700-000000000000}">
-  <dimension ref="A1:AW17"/>
+  <dimension ref="A1:AX17"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="6" max="49" width="9.140625" customWidth="1"/>
+  </cols>
   <sheetData>
-    <row r="1" spans="1:49" ht="39" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:50" ht="39" x14ac:dyDescent="0.25">
       <c r="A1" s="2" t="s">
         <v>663</v>
       </c>
@@ -7706,8 +7725,11 @@
       <c r="AW1" s="2" t="s">
         <v>696</v>
       </c>
-    </row>
-    <row r="2" spans="1:49" x14ac:dyDescent="0.25">
+      <c r="AX1" s="9" t="s">
+        <v>733</v>
+      </c>
+    </row>
+    <row r="2" spans="1:50" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
         <v>94</v>
       </c>
@@ -7855,8 +7877,11 @@
       <c r="AW2" s="8" t="s">
         <v>731</v>
       </c>
-    </row>
-    <row r="3" spans="1:49" x14ac:dyDescent="0.25">
+      <c r="AX2">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="3" spans="1:50" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
         <v>95</v>
       </c>
@@ -8004,8 +8029,11 @@
       <c r="AW3" s="8" t="s">
         <v>731</v>
       </c>
-    </row>
-    <row r="4" spans="1:49" x14ac:dyDescent="0.25">
+      <c r="AX3">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="4" spans="1:50" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
         <v>96</v>
       </c>
@@ -8153,8 +8181,11 @@
       <c r="AW4" s="8" t="s">
         <v>731</v>
       </c>
-    </row>
-    <row r="5" spans="1:49" x14ac:dyDescent="0.25">
+      <c r="AX4">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="5" spans="1:50" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
         <v>97</v>
       </c>
@@ -8302,8 +8333,11 @@
       <c r="AW5" s="8" t="s">
         <v>731</v>
       </c>
-    </row>
-    <row r="6" spans="1:49" x14ac:dyDescent="0.25">
+      <c r="AX5">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="6" spans="1:50" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
         <v>98</v>
       </c>
@@ -8451,8 +8485,11 @@
       <c r="AW6" s="8" t="s">
         <v>731</v>
       </c>
-    </row>
-    <row r="7" spans="1:49" x14ac:dyDescent="0.25">
+      <c r="AX6">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="7" spans="1:50" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
         <v>99</v>
       </c>
@@ -8600,8 +8637,11 @@
       <c r="AW7" s="8" t="s">
         <v>731</v>
       </c>
-    </row>
-    <row r="8" spans="1:49" x14ac:dyDescent="0.25">
+      <c r="AX7">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="8" spans="1:50" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
         <v>100</v>
       </c>
@@ -8749,8 +8789,11 @@
       <c r="AW8" s="8" t="s">
         <v>731</v>
       </c>
-    </row>
-    <row r="9" spans="1:49" x14ac:dyDescent="0.25">
+      <c r="AX8">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="9" spans="1:50" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
         <v>101</v>
       </c>
@@ -8898,8 +8941,11 @@
       <c r="AW9" s="8" t="s">
         <v>731</v>
       </c>
-    </row>
-    <row r="10" spans="1:49" x14ac:dyDescent="0.25">
+      <c r="AX9">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="10" spans="1:50" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
         <v>102</v>
       </c>
@@ -9047,8 +9093,11 @@
       <c r="AW10" s="8" t="s">
         <v>731</v>
       </c>
-    </row>
-    <row r="11" spans="1:49" x14ac:dyDescent="0.25">
+      <c r="AX10">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="11" spans="1:50" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
         <v>103</v>
       </c>
@@ -9196,8 +9245,11 @@
       <c r="AW11" s="8" t="s">
         <v>731</v>
       </c>
-    </row>
-    <row r="12" spans="1:49" x14ac:dyDescent="0.25">
+      <c r="AX11">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="12" spans="1:50" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
         <v>104</v>
       </c>
@@ -9345,8 +9397,11 @@
       <c r="AW12" s="8" t="s">
         <v>731</v>
       </c>
-    </row>
-    <row r="13" spans="1:49" x14ac:dyDescent="0.25">
+      <c r="AX12">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="13" spans="1:50" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
         <v>105</v>
       </c>
@@ -9494,8 +9549,11 @@
       <c r="AW13" s="8" t="s">
         <v>731</v>
       </c>
-    </row>
-    <row r="14" spans="1:49" x14ac:dyDescent="0.25">
+      <c r="AX13">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="14" spans="1:50" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
         <v>106</v>
       </c>
@@ -9643,8 +9701,11 @@
       <c r="AW14" s="8" t="s">
         <v>731</v>
       </c>
-    </row>
-    <row r="15" spans="1:49" x14ac:dyDescent="0.25">
+      <c r="AX14">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="15" spans="1:50" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
         <v>107</v>
       </c>
@@ -9792,8 +9853,11 @@
       <c r="AW15" s="8" t="s">
         <v>731</v>
       </c>
-    </row>
-    <row r="16" spans="1:49" x14ac:dyDescent="0.25">
+      <c r="AX15">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="16" spans="1:50" x14ac:dyDescent="0.25">
       <c r="A16" t="s">
         <v>108</v>
       </c>
@@ -9941,8 +10005,11 @@
       <c r="AW16" s="8" t="s">
         <v>731</v>
       </c>
-    </row>
-    <row r="17" spans="1:49" x14ac:dyDescent="0.25">
+      <c r="AX16">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="17" spans="1:50" x14ac:dyDescent="0.25">
       <c r="A17" t="s">
         <v>109</v>
       </c>
@@ -10089,6 +10156,9 @@
       </c>
       <c r="AW17" s="8" t="s">
         <v>731</v>
+      </c>
+      <c r="AX17">
+        <v>2</v>
       </c>
     </row>
   </sheetData>
